--- a/docs/tickets/CIVILYTICS_TICKETS.xlsx
+++ b/docs/tickets/CIVILYTICS_TICKETS.xlsx
@@ -10,10 +10,12 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Login" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Landing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Round-trip findings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Login'!$A$1:$M$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Landing'!$A$1:$M$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Round-trip findings'!$A$1:$M$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -457,9 +459,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3570,4 +3570,570 @@
   <autoFilter ref="A1:M29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="74" customWidth="1" min="7" max="7"/>
+    <col width="74" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Ticket ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Depends On</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Evidence / Source</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>WW-SET-BUG-001</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Config propagation</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>set_config writes the DB but never notifies the pipeline</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>config_routes.set_config commits a system_config row and stops. The pipeline reads ww:config:{key}_override from Redis, and today ONLY services/healer/main.py writes those keys. So a human changing a detection threshold in Settings is silently ignored by the live pipeline; only auto-remediation can retune it.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>After commit, set_config sets ww:config:{key}_override (which the pipeline already honours) or PUBLISHes ww:pipeline:commands. Changing Confidence Threshold changes pipeline behaviour within one poll cycle, verified by a pipeline log line.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>config_routes.py:50-66; healer/main.py:559,583; pipeline reads ww:config:*_override</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WW-ANL-BUG-002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Cards with no store</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>'Avg Response' and 'Resolution Status' render values no endpoint computes</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Neither card has an aggregator function or a worker producing the value. They display placeholder/zero.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Add aggregator functions (status counts from violation_events.status; response time from acknowledged_at - timestamp) or remove the cards. No card wired to nothing.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>AnalyticsView.tsx; aggregator.py has no such functions</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WW-ANL-003</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Orphan endpoint</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/analytics/by-camera has no card</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Endpoint exists and is tested but nothing in the UI renders it.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Add a per-camera breakdown card, or retire the endpoint.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>routes/analytics.py:27; AnalyticsView.tsx</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WW-ANL-004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Derived categories</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>No card for midnight-vehicle / daytime-work categories</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>The clustering feature writes violation_events.category via the categoriser (reports family). Categoriser not built, column is NULL, so no card can render it yet.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Once the categoriser runs, an Analytics card shows the four derived categories with counts, and uncategorised events are shown as a distinct 'uncategorised' bucket.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>WW-WRK-categoriser</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>plan-analytics-data.md; migration 009 category column</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>WW-HIS-BUG-005</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Event History</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Filters are fake</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Search, zone, severity, date range and repeat-offender never reach the SQL</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>GET /api/alerts is called with a flat limit=100. All filter controls are client-side or cosmetic, so the evidence archive cannot actually be queried.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Each filter passes through to the query: zone_id, severity, date range, status (all exist post-009). Results reflect the selected filters server-side.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>HistoryView.tsx (1 fetch, limit=100); routes/alerts.py list_alerts</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>WW-HIS-006</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Event History</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Pagination</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>No server pagination; 'Previous' does nothing</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>limit=100 is hardcoded and there is no offset/keyset. Older events past 100 are unreachable.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Keyset pagination on (timestamp, id). Previous/Next page through the full archive.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>WW-HIS-BUG-005</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>HistoryView.tsx</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>WW-SET-007</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Mockup page</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Chore</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Entire Settings view is a mockup</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>9 switches, 0 onChange, 0 fetch. Most rows have an existing backend (config/{key}, devices/*, reports/recipients, users/*, capture switch); three do not.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Each row wired to its endpoint. Delete SMS, Two-Factor and Repeat-Offender (no backend). Fix the storage-path default string: shows '/var/wastewatch/evidence' which is the wrong path (real /app/evidence) and the retired name.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>WW-SET-BUG-001</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>SettingsView.tsx: fetch=0 onChange=0; Settings:219 wrong path</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>